--- a/input/temp_file.xlsx
+++ b/input/temp_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,16 @@
           <t>finde_name</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>adeo_price</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>adeo_delivery</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -486,27 +496,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>148.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30 - 35 днейЗаказ до15:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>294.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4 дней</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AUTOPART Автодеталь</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>368.12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -526,27 +546,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2835.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30 - 35 днейЗаказ до15:45</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>5105.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4 дней</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Маслоприемник</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8155.75</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -566,27 +596,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>181.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Пpoклaдкa peзинoвaя</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200.28</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -606,27 +646,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>297.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>327.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Прокладка</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>299.57</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -646,27 +696,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>428.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>423.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Шестерня маслонасоса</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>453.3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -686,27 +746,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>220.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>223.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ПРОКЛАДКА</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -726,27 +796,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>172.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до15:45</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Пpокладка масл насоса</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>210.65</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -766,27 +846,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>333.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Прокладка маслонасоса 15188-75021 NOK</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>362.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -806,27 +896,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1335.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дняЗаказ до14:45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3308.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ФИЛЬТР САЛОННЫЙ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1572.67</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -846,27 +946,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>624.38</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Крепление глушителя</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>661.24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -886,27 +996,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>854.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>887.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>прокладка вых.системы</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>434.54</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -926,27 +1046,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3270.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3503.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Воздушный фильтр Toyota LAND CRUISER</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3587.42</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -966,27 +1096,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1100.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2675.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Фильтр воздушный Avantech</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>731.61</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1006,27 +1146,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>726.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3097.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Фильтр воздушный TOYOTA RAV-4 2.2D-4D (2ADFTV) 12- LEXUS GS 12-,IS 13-,RC 14- (17801-31170) JAPAN</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>862.06</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1046,27 +1196,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>227.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Прокладка клапана</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>253.95</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1086,27 +1246,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>559.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>5 - 7 дней</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>536.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4 дней</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ПРОКЛАДКА ДРОССЕЛЬНОЙ  ЗАСЛОНКИ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>718.76</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1296,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>399.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Прокладки ДВСTOYOTA</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>220.95</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1346,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>460.35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>587.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Прокладка</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>549.32</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1206,27 +1396,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>356.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>253.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Кольцо дроселя</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1246,27 +1446,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>14197.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до14:30</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>13791.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Насос топливный</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15035.88</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1286,27 +1496,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>245.28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>КОЛЬЦО</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>262.12</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1326,27 +1546,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2586.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3113.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Фильтр топливный 2339051030</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>527.72</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1366,27 +1596,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1130.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Фильтр топливный грубой очистки</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1055.43</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1406,27 +1646,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>107.76</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Кольцо форсунки</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1446,27 +1696,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>263.05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>49 - 50 днейЗаказ до15:15</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>708.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Шайба пластиковая</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>729.52</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1486,27 +1746,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Кольцо резиновое 23258-36010 NX</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>191.43</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1526,27 +1796,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1980.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до16:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1936.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Фильтр топливный</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>453.16</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1846,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2975.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3557.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Фильтр топливный TOYOTA Land Cruiser 200 (08-) (4.5TD) MEGAPOWER (ан. 23390-51070/23390-YZZA4) 110-15-012</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1606,27 +1896,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>7097.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до16:00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>6596.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Фильтр топливный TOYOTA Land Cruiser (21-) OE</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7553.77</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1646,27 +1946,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Прокладка</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>132.05</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1686,27 +1996,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>263.65</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>269.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Крышка шкива генератора AZN8050DD (274160W050) KRAUF</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>275.97</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1726,27 +2046,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>149.32</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>КОЛЬЦО</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>105.75</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1766,27 +2096,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2298.31</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4564.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ЩеточныйУзел SHN5190ZD/MC/SBH6024S/ стартер,1TR,2TR,3RZ TESLA</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3542.74</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1806,27 +2146,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>461.98</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>468.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>КОНТАКТ МЕТАЛЛИЧЕСКИЙ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>497.43</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1846,27 +2196,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1819.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1940.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ВИЛКА СЦЕПЛЕНИЯ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1948.53</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1886,27 +2246,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>297.0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>295.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Накладка педали тормоза и сцепления 300 (Е-3/4)</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>381.63</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1926,27 +2296,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>9216.9</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до14:30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>12047.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ФЛАНЕЦ ДВИГАТЕЛЯ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>9761.03</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1966,27 +2346,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2871.0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3141.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Фильтр АКПП TOYOTA</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3151.17</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2006,27 +2396,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>144.67</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>МЕРНАЯ ТРУБКА 47694A U660E/U661E</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>144.17</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2046,27 +2446,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Прокладка поддона АКПП</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>323.5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2086,27 +2496,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1782.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2812.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Комплект фильтра вариатора (с кольцом фильтра и прокладкой поддона) MASUMA Japan</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2579.18</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2126,27 +2546,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3100.9</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3284.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Фильтр масляный АКПП</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3372.51</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2166,27 +2596,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3757.6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до14:30</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3728.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Фильтр масляный акпп</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4011.54</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2206,27 +2646,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>515.9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>630.0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Slinger Drive Pinion</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>556.11</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2246,27 +2696,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>627.0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>712.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Втулка хвостовика</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>680.74</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2286,27 +2746,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>912.36</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>988.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Втулка хвостовика</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>967.96</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2326,27 +2796,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>594.96</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ПРОКЛАДКА ПЕРЕДН.ДИФ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>635.35</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2366,27 +2846,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>264.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>42 - 48 дней</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Хомут</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>570.82</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2896,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>366.1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>624.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Прокладка диффе</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>391.6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2446,27 +2946,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>363.3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>357.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Прокладка дифферинциала</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>384.75</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2486,27 +2996,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>141.4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Болт крепежный ступицы заднего моста TOYOTA DYNA/TOYOTACE/LAND CRUISER MANY</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>104.29</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2526,27 +3046,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1880.34</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1934.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Трубка вентиляции LC100</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1896.52</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2566,27 +3096,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3457.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>8 - 10 дней</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4106.0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>5 дней</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Ступица в сборе, задняя</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4028.36</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2606,27 +3146,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>548.09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>574.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ШАЙБА МЕТАЛЛИЧЕСКАЯ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>580.45</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2646,27 +3196,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1242.84</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1329.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ВТУЛКА МЕТАЛЛИЧЕСКАЯ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1258.23</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2686,27 +3246,37 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Прокладка</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>46.93</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2726,27 +3296,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1127.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1246.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Пыльники деталей подвески Avantech (Кратность 10 шт.)</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1196.39</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2766,27 +3346,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>193.6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>255.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>КОЛПАК СТУПИЦЫ КОЛЕСА</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>220.62</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2806,27 +3396,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1065.43</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1453.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Ротор ABS TOYOTA DYNA FORTUNER HIACE REGIUSACE HILUX LAND CRUISER TUNDRA..</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1128.33</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2846,27 +3446,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Гайка п. ступицы</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>321.21</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2886,27 +3496,37 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>12820.86</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до14:30</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>12250.0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ТОРМОЗНОЙ ДИСК</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>11882.83</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2926,27 +3546,37 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2345.32</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2968.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Наконечник рулевой тяги 555</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2452.21</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2966,27 +3596,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до14:30</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>265.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>ВТУЛКА РУЛ.КОЛОНКИ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>279.59</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3006,27 +3646,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1511.92</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1494.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ВТУЛКА РЕЗИНОВАЯ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1601.17</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3046,27 +3696,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1152.8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1150.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Поршень тормозного суппорта Gbrake</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1251.15</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3086,27 +3746,37 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>141.4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ШТИФТ ()</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>98.13</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3126,27 +3796,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>33236.5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 деньЗаказ до14:30</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>30944.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Рычаг подвески JETT</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>35186.72</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3166,27 +3846,37 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1089.0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>42 - 48 дней</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1484.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>4 дней</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>ОТБОЙНИК РЕЗИНОВЫЙ</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1526.85</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3206,27 +3896,37 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>537.24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>598.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Отбойник амортизатора переднего</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>568.96</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3246,27 +3946,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>542.3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>665.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>ОТБОЙНИК АМОРТИЗАТОРА</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>600.5</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3286,27 +3996,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>491.28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>493.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ОТБОЙНИК АМОРТИЗАТОРА</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>532.51</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3326,27 +4046,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>562.14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>549.0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Отбойник амортизатора переднего</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>601.29</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3366,27 +4096,37 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>766.15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>788.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Отбойник передней стойки TOYOTA CAMRY ACV3# MCV3# 0106</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3406,27 +4146,37 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>765.48</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>923.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Болт с эксцентриком</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>810.67</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3446,27 +4196,37 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>533.28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>570.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Болт (комплект) с эксцентриком</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>564.77</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3486,27 +4246,37 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>638.0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>626.0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Эксцентрик</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>675.67</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3526,27 +4296,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>955.9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Шайба эксцентриковая</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>876.04</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3566,27 +4346,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1361.56</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Втулка амортизатора</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1456.36</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3606,27 +4396,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>508.2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>621.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Опора кузова</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>564.77</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3646,27 +4446,37 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1835.37</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>3422.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1 дней</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>SPARE PART</t>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1845.79</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -3709,6 +4519,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3749,6 +4569,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3789,6 +4619,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3829,6 +4669,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3869,6 +4719,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3909,6 +4769,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3949,6 +4819,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3989,6 +4869,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4029,6 +4919,16 @@
           <t>None</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4067,6 +4967,16 @@
       <c r="H91" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>

--- a/input/temp_file.xlsx
+++ b/input/temp_file.xlsx
@@ -606,12 +606,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>226.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>10000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1 - 2 дняЗаказ до14:45</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3308.0</t>
+          <t>1234.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>618.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3503.0</t>
+          <t>3171.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2675.0</t>
+          <t>817.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>399.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>587.0</t>
+          <t>504.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>366.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до14:30</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3113.0</t>
+          <t>3295.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>800</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>191.43</t>
+          <t>381.63</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3557.0</t>
+          <t>2897.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4564.0</t>
+          <t>2994.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3542.74</t>
+          <t>3242.2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>468.0</t>
+          <t>455.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1940.0</t>
+          <t>1768.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>699</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2301,17 +2301,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до14:30</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12047.0</t>
+          <t>9657.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3284.0</t>
+          <t>3463.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до14:30</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3728.0</t>
+          <t>3659.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>504.0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>712.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>4 дней</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>624.0</t>
+          <t>365.0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>357.0</t>
+          <t>378.0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1934.0</t>
+          <t>1750.0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>574.0</t>
+          <t>495.0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1329.0</t>
+          <t>1204.0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1246.0</t>
+          <t>1102.0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>255.0</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1453.0</t>
+          <t>1028.0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>303.3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>1 - 3 дня</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до14:30</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2968.0</t>
+          <t>2437.0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до14:30</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>265.0</t>
+          <t>374.0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>93</v>
+        <v>500</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -3656,12 +3656,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1494.0</t>
+          <t>1465.0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1150.0</t>
+          <t>1123.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до14:30</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>598.0</t>
+          <t>528.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>665.0</t>
+          <t>533.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>788.0</t>
+          <t>753.0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>923.0</t>
+          <t>767.0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>600</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4206,12 +4206,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>570.0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>725.0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>1332.0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>621.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3422.0</t>
+          <t>3321.0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">

--- a/input/temp_file.xlsx
+++ b/input/temp_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>emex_price</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>emex_delivery</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>adeo_price</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>adeo_delivery</t>
         </is>
@@ -496,22 +506,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>148.17</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30 - 35 днейЗаказ до15:45</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -521,12 +531,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>368.12</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -551,7 +571,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30 - 35 днейЗаказ до15:45</t>
+          <t>30 - 36 дней</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -571,12 +591,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8155.75</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -621,10 +651,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>200.28</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -656,12 +696,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>327.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -671,10 +711,20 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>299.57</t>
+          <t>404</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>301.05</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -721,10 +771,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>453.3</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -771,10 +831,20 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -801,7 +871,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до15:45</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -811,7 +881,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -821,10 +891,20 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>210.65</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>211.7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -871,10 +951,20 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>362.3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -921,10 +1011,20 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>3640</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>1572.67</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -956,7 +1056,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>618.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -971,10 +1071,20 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>661.24</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1021,10 +1131,20 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>434.54</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1056,7 +1176,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3171.0</t>
+          <t>3416.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1071,10 +1191,20 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>3797</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>3587.42</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1106,7 +1236,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>817.0</t>
+          <t>2308.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1121,10 +1251,20 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>3763</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>731.61</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1171,10 +1311,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>862.06</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1206,7 +1356,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1221,10 +1371,20 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>253.95</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1271,10 +1431,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>718.76</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1306,7 +1476,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1321,10 +1491,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>220.95</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1371,10 +1551,20 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>549.32</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1421,10 +1611,20 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1471,10 +1671,20 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>16963</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>15035.88</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1521,10 +1731,20 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>262.12</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1556,12 +1776,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3295.0</t>
+          <t>2514.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1571,10 +1791,20 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>527.72</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1606,12 +1836,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>1093.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1621,10 +1851,20 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>1055.43</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1656,7 +1896,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1671,10 +1911,20 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1701,17 +1951,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>49 - 50 днейЗаказ до15:15</t>
+          <t>49 - 51 день</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>708.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>4 дней</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1721,10 +1971,20 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>729.52</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1771,10 +2031,20 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>381.63</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1801,7 +2071,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до16:00</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1821,10 +2091,20 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>453.16</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1871,10 +2151,20 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>3470</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>3150</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1901,7 +2191,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1 деньЗаказ до16:00</t>
+          <t>1 - 2 дня</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1921,10 +2211,20 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>7553.77</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1956,12 +2256,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1971,10 +2271,20 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>132.05</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2021,10 +2331,20 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>275.97</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2056,12 +2376,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2071,10 +2391,20 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>105.75</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2106,7 +2436,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2994.0</t>
+          <t>3455.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2121,10 +2451,20 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>3242.2</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2171,10 +2511,20 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>497.43</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2206,7 +2556,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1768.0</t>
+          <t>1780.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2221,10 +2571,20 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>1948.53</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2271,10 +2631,20 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>381.63</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2306,7 +2676,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9657.0</t>
+          <t>8956.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2321,10 +2691,20 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>14819</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>9761.03</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2346,7 +2726,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2871.0</t>
+          <t>2964.5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2356,12 +2736,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3141.0</t>
+          <t>2881.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2371,10 +2751,20 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>4299</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>3151.17</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2406,7 +2796,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2421,10 +2811,20 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>144.17</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2471,10 +2871,20 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>323.5</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2506,7 +2916,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2812.0</t>
+          <t>2951.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2521,10 +2931,20 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>2579.18</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2556,12 +2976,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3463.0</t>
+          <t>2651.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2571,10 +2991,20 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>3593</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>3372.51</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2621,10 +3051,20 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>7138</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>4011.54</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2671,10 +3111,20 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>556.11</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2696,7 +3146,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>627.0</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2706,7 +3156,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2721,10 +3171,20 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>680.74</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2756,12 +3216,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>988.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2771,10 +3231,20 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>967.96</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>972.78</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2811,7 +3281,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2821,10 +3291,20 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>635.35</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2871,10 +3351,20 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>570.82</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2921,10 +3411,20 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>391.6</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2946,22 +3446,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>363.3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2971,12 +3471,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>384.75</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3521,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>2 дней</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3021,10 +3531,20 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>104.29</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3071,10 +3591,20 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>1896.52</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3096,22 +3626,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3457.3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>8 - 10 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4106.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3121,12 +3651,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4028.36</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3686,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>548.09</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>495.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3171,12 +3711,22 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>580.45</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3196,22 +3746,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1242.84</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1204.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3221,12 +3771,22 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1258.23</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3246,22 +3806,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3271,12 +3831,22 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3296,22 +3866,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1127.5</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1102.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3321,12 +3891,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1196.39</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3346,22 +3926,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>193.6</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>195.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3371,12 +3951,22 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>220.62</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3986,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1065.43</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1028.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3421,12 +4011,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1128.33</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3446,22 +4046,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>303.3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3471,12 +4071,22 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>321.21</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3496,22 +4106,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12820.86</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>12250.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3521,12 +4131,22 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>11882.83</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3546,22 +4166,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2345.32</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2437.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3571,12 +4191,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2452.21</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3596,22 +4226,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3621,12 +4251,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>279.59</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3646,22 +4286,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1511.92</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1465.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3671,12 +4311,22 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1601.17</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3696,22 +4346,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1152.8</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3721,12 +4371,22 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1251.15</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3746,22 +4406,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>141.4</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3771,12 +4431,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3796,22 +4466,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>33236.5</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>30944.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3821,12 +4491,22 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>35186.72</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3846,22 +4526,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1089.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>42 - 48 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1484.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3871,12 +4551,22 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1526.85</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3896,22 +4586,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>537.24</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>528.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3921,12 +4611,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>568.96</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3946,22 +4646,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>542.3</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>533.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3971,12 +4671,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>600.5</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -3996,22 +4706,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>491.28</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>493.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4021,12 +4731,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>532.51</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4046,22 +4766,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>562.14</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>549.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4071,12 +4791,22 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>601.29</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4096,22 +4826,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>766.15</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>753.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4121,12 +4851,22 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4146,22 +4886,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>765.48</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4171,12 +4911,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>810.67</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4196,22 +4946,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>533.28</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1 - 3 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4221,12 +4971,22 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>564.77</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4246,22 +5006,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>626.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4271,12 +5031,22 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>675.67</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4296,22 +5066,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>955.9</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>725.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4321,12 +5091,22 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>876.04</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4346,22 +5126,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1361.56</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1332.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4371,12 +5151,22 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1456.36</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4396,22 +5186,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>508.2</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4421,12 +5211,22 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>564.77</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4446,22 +5246,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1835.37</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1 - 2 дня</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>3321.0</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2 дней</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4471,12 +5271,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1845.79</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>n</t>
         </is>
       </c>
     </row>
@@ -4529,6 +5339,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4579,6 +5399,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4629,6 +5459,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4679,6 +5519,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4729,6 +5579,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4779,6 +5639,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4829,6 +5699,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4879,6 +5759,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4929,6 +5819,16 @@
           <t>n</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4975,6 +5875,16 @@
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>n</t>
         </is>
